--- a/BWI/bestwine_output/bestwine_Kenya.xlsx
+++ b/BWI/bestwine_output/bestwine_Kenya.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -5973,6 +5973,83 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Siddham Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Siddham Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>47054</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi County</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Premier Industrial Park, Warehouse No.1, Baba Dogo</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>00100</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://siddhambeverages.com</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>info@siddhambeverages.com</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Kenya.xlsx
+++ b/BWI/bestwine_output/bestwine_Kenya.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA54"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6050,6 +6050,176 @@
       <c r="Z54" s="2" t="inlineStr"/>
       <c r="AA54" s="2" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquor House </t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>168248</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Kiambu</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Kasarini Trading Center Lr No. 22402 Kiambu Road</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://liquorhouse.delivery</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>301974</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>sales@liquorhouse.delivery</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>BN-9PCEVXY</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/liquorhouse254</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/liquorhouse254/</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@liquorhouse</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr"/>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>MEGA LIQUOR DISTRIBUTORS LIMITED</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>168247</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Nairobi</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Tom Mboya S Street Plot No. 209/1127</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://thewhiskyshop.co.ke, https://www.megawines.co.ke</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2113815</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>info@megawines.co.ke</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>C.121263</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Omwakabin_Okoti</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
